--- a/data/trans_bre/IMC_inf_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_R2-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,5; -3,05</t>
+          <t>-23,85; -4,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,36; 3,82</t>
+          <t>-18,12; 4,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 3,79</t>
+          <t>-19,83; 3,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,41; 5,37</t>
+          <t>-19,67; 5,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,79; -6,98</t>
+          <t>-46,08; -10,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,82; 10,03</t>
+          <t>-32,74; 11,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-34,51; 8,06</t>
+          <t>-35,56; 7,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,01; 18,44</t>
+          <t>-43,25; 18,53</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,05; -2,35</t>
+          <t>-19,08; -2,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,74; -5,73</t>
+          <t>-23,51; -4,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,03; -7,88</t>
+          <t>-24,58; -8,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,26; -4,06</t>
+          <t>-21,53; -3,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,63; -5,24</t>
+          <t>-36,37; -5,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,35; -11,08</t>
+          <t>-38,97; -8,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-49,83; -20,06</t>
+          <t>-50,0; -21,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,36; -11,38</t>
+          <t>-47,93; -10,33</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-22,2; -1,75</t>
+          <t>-20,83; -2,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,66; 4,67</t>
+          <t>-16,85; 3,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,78; 4,42</t>
+          <t>-14,45; 3,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-27,35; 0,38</t>
+          <t>-26,61; 0,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-44,06; -3,62</t>
+          <t>-42,99; -5,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,4; 11,28</t>
+          <t>-32,36; 9,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-34,0; 13,0</t>
+          <t>-34,37; 10,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-61,99; 0,92</t>
+          <t>-59,96; -0,18</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 3,62</t>
+          <t>-14,95; 3,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 5,51</t>
+          <t>-13,41; 5,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-17,92; 0,09</t>
+          <t>-17,97; 1,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 1,29</t>
+          <t>-18,66; 1,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,85; 10,13</t>
+          <t>-32,63; 9,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,37; 12,75</t>
+          <t>-25,5; 13,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,5; 0,33</t>
+          <t>-35,67; 3,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,72; 5,07</t>
+          <t>-45,16; 5,37</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,42; -5,16</t>
+          <t>-14,62; -5,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,5; -3,98</t>
+          <t>-13,62; -3,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,65; -5,35</t>
+          <t>-14,63; -4,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,87; -5,18</t>
+          <t>-15,83; -4,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,69; -11,96</t>
+          <t>-30,91; -13,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,27; -8,09</t>
+          <t>-25,56; -6,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,02; -12,61</t>
+          <t>-31,25; -11,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-41,14; -15,25</t>
+          <t>-38,97; -13,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_R2-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado</t>
+          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,85; -4,55</t>
+          <t>-23,7; -4,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 4,88</t>
+          <t>-18,91; 3,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,83; 3,36</t>
+          <t>-21,58; 3,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 5,86</t>
+          <t>-20,33; 5,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-46,08; -10,7</t>
+          <t>-46,13; -10,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,74; 11,08</t>
+          <t>-33,8; 8,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-35,56; 7,33</t>
+          <t>-37,54; 9,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,25; 18,53</t>
+          <t>-43,97; 16,91</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,08; -2,71</t>
+          <t>-19,24; -2,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,51; -4,38</t>
+          <t>-23,8; -6,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,58; -8,92</t>
+          <t>-24,89; -8,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,53; -3,77</t>
+          <t>-21,96; -4,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,37; -5,96</t>
+          <t>-36,15; -5,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,97; -8,3</t>
+          <t>-39,74; -11,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-50,0; -21,95</t>
+          <t>-50,93; -20,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,93; -10,33</t>
+          <t>-47,87; -11,63</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,83; -2,05</t>
+          <t>-21,72; -2,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 3,93</t>
+          <t>-16,34; 4,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 3,85</t>
+          <t>-14,47; 4,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-26,61; 0,12</t>
+          <t>-27,74; 0,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-42,99; -5,4</t>
+          <t>-43,2; -5,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,36; 9,49</t>
+          <t>-31,52; 9,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-34,37; 10,65</t>
+          <t>-33,03; 14,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-59,96; -0,18</t>
+          <t>-62,59; -2,42</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,95; 3,38</t>
+          <t>-14,04; 2,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 5,69</t>
+          <t>-14,59; 5,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 1,45</t>
+          <t>-16,44; 1,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 1,53</t>
+          <t>-17,61; 1,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,63; 9,97</t>
+          <t>-31,58; 8,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,5; 13,27</t>
+          <t>-27,13; 12,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,67; 3,73</t>
+          <t>-33,12; 3,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-45,16; 5,37</t>
+          <t>-42,8; 4,79</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,62; -5,7</t>
+          <t>-14,45; -5,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,62; -3,32</t>
+          <t>-13,6; -3,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,63; -4,48</t>
+          <t>-14,87; -5,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,83; -4,76</t>
+          <t>-16,53; -5,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,91; -13,46</t>
+          <t>-30,44; -13,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,56; -6,95</t>
+          <t>-25,63; -6,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,25; -11,01</t>
+          <t>-31,9; -12,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-38,97; -13,84</t>
+          <t>-40,01; -13,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_R2-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-7,44</t>
+          <t>-10,45</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-19,63%</t>
+          <t>-26,02%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,7; -4,49</t>
+          <t>-23,5; -3,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 3,88</t>
+          <t>-19,36; 3,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,58; 3,77</t>
+          <t>-18,67; 3,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,33; 5,6</t>
+          <t>-22,26; 2,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-46,13; -10,1</t>
+          <t>-45,79; -6,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,8; 8,39</t>
+          <t>-34,82; 10,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-37,54; 9,15</t>
+          <t>-34,51; 8,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,97; 16,91</t>
+          <t>-47,25; 6,08</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-31,52%</t>
+          <t>-31,36%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,24; -2,56</t>
+          <t>-19,05; -2,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,8; -6,19</t>
+          <t>-23,74; -5,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,89; -8,24</t>
+          <t>-24,03; -7,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,96; -4,26</t>
+          <t>-22,33; -4,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,15; -5,55</t>
+          <t>-36,63; -5,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,74; -11,72</t>
+          <t>-39,35; -11,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-50,93; -20,16</t>
+          <t>-49,83; -20,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,87; -11,63</t>
+          <t>-48,09; -10,74</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-11,58</t>
+          <t>-8,94</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-29,76%</t>
+          <t>-22,85%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,72; -2,3</t>
+          <t>-22,2; -1,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 4,46</t>
+          <t>-15,66; 4,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 4,65</t>
+          <t>-14,78; 4,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-27,74; 0,32</t>
+          <t>-20,35; 1,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-43,2; -5,24</t>
+          <t>-44,06; -3,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,52; 9,81</t>
+          <t>-29,4; 11,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-33,03; 14,74</t>
+          <t>-34,0; 13,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-62,59; -2,42</t>
+          <t>-43,69; 5,72</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-8,73</t>
+          <t>-9,89</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-23,58%</t>
+          <t>-27,26%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 2,82</t>
+          <t>-14,1; 3,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 5,37</t>
+          <t>-13,64; 5,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 1,37</t>
+          <t>-17,92; 0,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 1,52</t>
+          <t>-19,1; -0,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,58; 8,2</t>
+          <t>-31,85; 10,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,13; 12,26</t>
+          <t>-25,37; 12,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,12; 3,4</t>
+          <t>-35,5; 0,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,8; 4,79</t>
+          <t>-47,33; -1,68</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-10,67</t>
+          <t>-10,84</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-27,36%</t>
+          <t>-27,52%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,45; -5,91</t>
+          <t>-14,42; -5,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,6; -3,44</t>
+          <t>-13,5; -3,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,87; -5,13</t>
+          <t>-14,65; -5,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,53; -5,1</t>
+          <t>-15,8; -5,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,44; -13,47</t>
+          <t>-30,69; -11,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,63; -6,89</t>
+          <t>-25,27; -8,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,9; -12,12</t>
+          <t>-31,02; -12,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-40,01; -13,9</t>
+          <t>-37,33; -15,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_R2-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -522,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as</t>
+          <t>Población con sobrepeso u obesidad declarado por madres/padres</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-13,84</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-7,19</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-8,02</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-10,45</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-29,38%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-14,52%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-15,99%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-26,02%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-13.83806613055269</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-7.18571313944617</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-8.016241853979162</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-10.445665845538</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.2938256793510976</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.1452283779782886</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.1598501362232796</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.2601940047594167</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-23,5; -3,05</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-19,36; 3,82</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-18,67; 3,79</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-22,26; 2,18</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-45,79; -6,98</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-34,82; 10,03</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-34,51; 8,06</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-47,25; 6,08</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-23.50372529235934</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-19.36484534282879</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-18.67135686254416</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-22.26444307968854</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.4578718845183693</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.3482392565828606</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.345146014556152</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.4725339328583353</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>-3.049767652931354</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.821053427483199</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.79064391502803</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>2.182542471170338</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>-0.06975246512900757</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.1002548503772249</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.08062396754351819</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.06079248751117173</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-10,82</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-14,74</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-16,58</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-12,94</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-22,29%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-26,47%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-36,74%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-31,36%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-19,05; -2,35</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-23,74; -5,73</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-24,03; -7,88</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-22,33; -4,25</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-36,63; -5,24</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-39,35; -11,08</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-49,83; -20,06</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-48,09; -10,74</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-10.81740575853549</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-14.74202836491034</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-16.57567822152841</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-12.94291879922043</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.222874124225766</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2647232824317035</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.3673629390466222</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.3136309446110955</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-11,64</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-6,23</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,74</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-8,94</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-25,86%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-13,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-12,24%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-22,85%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-19.05240891500473</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-23.73815068968725</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-24.02669751151026</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-22.33016869269389</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.366298104853434</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3935074791951829</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4982610725377628</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.4808957503752272</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-22,2; -1,75</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-15,66; 4,67</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-14,78; 4,42</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-20,35; 1,65</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-44,06; -3,62</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-29,4; 11,28</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-34,0; 13,0</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-43,69; 5,72</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-2.349834254788296</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>-5.727370897150741</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>-7.881007743809882</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>-4.250551448408362</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-0.0523816904799907</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.1107705028757029</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>-0.2005577225713598</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>-0.1074314593975286</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-5,72</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-4,0</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-8,24</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-9,89</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-13,91%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-8,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-18,02%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-27,26%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-11.63602425559997</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-6.234963223733459</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-4.73618379868605</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-8.942932629694155</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.2586483427889976</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.1320522104791283</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.12239260098046</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.2284732055918983</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-14,1; 3,62</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-13,64; 5,51</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-17,92; 0,09</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-19,1; -0,34</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-31,85; 10,13</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-25,37; 12,75</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-35,5; 0,33</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-47,33; -1,68</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-22.20285812445609</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-15.66051649304034</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-14.78381772899856</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-20.3485199489987</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.4406386724477326</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.293978938364275</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.3399671258173709</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.4369461767503146</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-1.75452212863608</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.674367813782702</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.42245358232658</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1.648315175903882</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>-0.03617391638989341</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.1127856220360358</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.1300047070912693</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.05718683428195459</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-5.719823480171627</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-3.997935039506662</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-8.238071334489783</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-9.889493945541062</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1391274670052901</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.08296868247485782</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.1802176921609257</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.2726015840177892</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-14.10180839964801</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-13.64021559627845</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-17.91711007907425</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-19.10101729396324</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3184803862681648</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2536578748761685</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.3549704753431187</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.4732737673682791</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3.618187843163581</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>5.507987618557224</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.08726741876831165</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-0.3429137406418411</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1012604793898593</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1275074034360827</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.003308267838679147</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>-0.01676837018674824</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-10,18</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-8,33</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-9,85</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-10,84</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-22,41%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-16,5%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-22,02%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-27,52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-14,42; -5,16</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-13,5; -3,98</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-14,65; -5,35</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-15,8; -5,79</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-30,69; -11,96</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-25,27; -8,09</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-31,02; -12,61</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-37,33; -15,87</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-10.17690067285283</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-8.328184433778269</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-9.850454737613596</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-10.83525572403882</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.2240672304047215</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.1649716222927928</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.2202378907336141</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.2751886093047166</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-14.42132587158736</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-13.49891268107203</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-14.65309017052844</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-15.79542258165106</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.3068717838752523</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2527003554966082</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.3102486501396552</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.3733012769993489</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>-5.159110482671275</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-3.984103319428525</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-5.350902873224721</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-5.788945940171785</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-0.1195547808536363</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>-0.08087279154362183</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>-0.1261108160223352</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>-0.1587198492215738</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
